--- a/word-monitor-sitemap/report/history/keyword-table-20260710-133103.xlsx
+++ b/word-monitor-sitemap/report/history/keyword-table-20260710-133103.xlsx
@@ -54,12 +54,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +451,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-10T15:31:14</t>
+          <t>2026-07-10T17:29:03</t>
         </is>
       </c>
     </row>
@@ -503,8 +514,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -579,158 +590,209 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>block sort jigsaw puzzle journey</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/cz/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/de/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/es/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/fi/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/gr/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/kr/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/pl/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/ru/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/se/game/block-sort---jigsaw-puzzle-journey</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/cz/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/de/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/es/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/fi/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/gr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/kr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/pl/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/ru/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/se/game/block-sort---jigsaw-puzzle-journey</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>downhill racer bvk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/downhill-racer-bvk | https://www.crazygames.com/es/game/downhill-racer-bvk | https://www.crazygames.com/fi/game/downhill-racer-bvk | https://www.crazygames.com/gr/game/downhill-racer-bvk | https://www.crazygames.com/kr/game/downhill-racer-bvk | https://www.crazygames.com/pl/game/downhill-racer-bvk | https://www.crazygames.com/se/game/downhill-racer-bvk</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/downhill-racer-bvk
+https://www.crazygames.com/es/game/downhill-racer-bvk
+https://www.crazygames.com/fi/game/downhill-racer-bvk
+https://www.crazygames.com/gr/game/downhill-racer-bvk
+https://www.crazygames.com/kr/game/downhill-racer-bvk
+https://www.crazygames.com/pl/game/downhill-racer-bvk
+https://www.crazygames.com/se/game/downhill-racer-bvk</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>nightfall survivors imo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/nightfall-survivors-imo | https://www.crazygames.com/br/game/nightfall-survivors-imo | https://www.crazygames.com/cz/game/nightfall-survivors-imo | https://www.crazygames.com/de/game/nightfall-survivors-imo | https://www.crazygames.com/es/game/nightfall-survivors-imo | https://www.crazygames.com/fi/game/nightfall-survivors-imo | https://www.crazygames.com/gr/game/nightfall-survivors-imo | https://www.crazygames.com/hu/game/nightfall-survivors-imo | https://www.crazygames.com/kr/game/nightfall-survivors-imo | https://www.crazygames.com/pl/game/nightfall-survivors-imo | https://www.crazygames.com/ro/game/nightfall-survivors-imo | https://www.crazygames.com/ru/game/nightfall-survivors-imo | https://www.crazygames.com/se/game/nightfall-survivors-imo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/nightfall-survivors-imo
+https://www.crazygames.com/br/game/nightfall-survivors-imo
+https://www.crazygames.com/cz/game/nightfall-survivors-imo
+https://www.crazygames.com/de/game/nightfall-survivors-imo
+https://www.crazygames.com/es/game/nightfall-survivors-imo
+https://www.crazygames.com/fi/game/nightfall-survivors-imo
+https://www.crazygames.com/gr/game/nightfall-survivors-imo
+https://www.crazygames.com/hu/game/nightfall-survivors-imo
+https://www.crazygames.com/kr/game/nightfall-survivors-imo
+https://www.crazygames.com/pl/game/nightfall-survivors-imo
+https://www.crazygames.com/ro/game/nightfall-survivors-imo
+https://www.crazygames.com/ru/game/nightfall-survivors-imo
+https://www.crazygames.com/se/game/nightfall-survivors-imo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>pixel world uyv</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/pixel-world-uyv | https://www.crazygames.com/es/game/pixel-world-uyv | https://www.crazygames.com/fi/game/pixel-world-uyv | https://www.crazygames.com/gr/game/pixel-world-uyv | https://www.crazygames.com/kr/game/pixel-world-uyv | https://www.crazygames.com/pl/game/pixel-world-uyv | https://www.crazygames.com/se/game/pixel-world-uyv</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/pixel-world-uyv
+https://www.crazygames.com/es/game/pixel-world-uyv
+https://www.crazygames.com/fi/game/pixel-world-uyv
+https://www.crazygames.com/gr/game/pixel-world-uyv
+https://www.crazygames.com/kr/game/pixel-world-uyv
+https://www.crazygames.com/pl/game/pixel-world-uyv
+https://www.crazygames.com/se/game/pixel-world-uyv</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>the flowers merge and sell bouquets</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/cz/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/de/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/es/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/fi/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/gr/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/kr/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/pl/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/ru/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/se/game/the-flowers-merge-and-sell-bouquets</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/cz/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/de/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/es/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/fi/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/gr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/kr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/pl/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/ru/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/se/game/the-flowers-merge-and-sell-bouquets</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>travel merge</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://poki.com/en/g/travel-merge</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>unscrambled</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/unscrambled | https://www.crazygames.com/cz/game/unscrambled | https://www.crazygames.com/de/game/unscrambled | https://www.crazygames.com/es/game/unscrambled | https://www.crazygames.com/fi/game/unscrambled | https://www.crazygames.com/gr/game/unscrambled | https://www.crazygames.com/kr/game/unscrambled | https://www.crazygames.com/pl/game/unscrambled | https://www.crazygames.com/ru/game/unscrambled | https://www.crazygames.com/se/game/unscrambled</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/unscrambled
+https://www.crazygames.com/cz/game/unscrambled
+https://www.crazygames.com/de/game/unscrambled
+https://www.crazygames.com/es/game/unscrambled
+https://www.crazygames.com/fi/game/unscrambled
+https://www.crazygames.com/gr/game/unscrambled
+https://www.crazygames.com/kr/game/unscrambled
+https://www.crazygames.com/pl/game/unscrambled
+https://www.crazygames.com/ru/game/unscrambled
+https://www.crazygames.com/se/game/unscrambled</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L8"/>
